--- a/StructureDefinition-heartland-careplan.xlsx
+++ b/StructureDefinition-heartland-careplan.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/StructureDefinition/heartland-careplan</t>
+    <t>https://fhir.heartlandprotocol.org/StructureDefinition/heartland-careplan</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T15:03:58-04:00</t>
+    <t>2026-04-16T15:20:02-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -462,7 +462,7 @@
     <t>facilityTier</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://heartlandprotocol.org/fhir/StructureDefinition/heartland-facility-tier}
+    <t xml:space="preserve">Extension {https://fhir.heartlandprotocol.org/StructureDefinition/heartland-facility-tier}
 </t>
   </si>
   <si>
@@ -482,7 +482,7 @@
     <t>monitoringTrack</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://heartlandprotocol.org/fhir/StructureDefinition/heartland-monitoring-track-ext}
+    <t xml:space="preserve">Extension {https://fhir.heartlandprotocol.org/StructureDefinition/heartland-monitoring-track-ext}
 </t>
   </si>
   <si>
@@ -761,7 +761,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://heartlandprotocol.org/fhir/StructureDefinition/heartland-patient|Patient)
+    <t xml:space="preserve">Reference(https://fhir.heartlandprotocol.org/StructureDefinition/heartland-patient|Patient)
 </t>
   </si>
   <si>
